--- a/mrp-panel-enaex/mrp-panel-enaex/data/ME5A/ME5A.XLSX
+++ b/mrp-panel-enaex/mrp-panel-enaex/data/ME5A/ME5A.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="355">
   <si>
     <t>Material</t>
   </si>
@@ -58,6 +58,528 @@
     <t>Status tratamiento</t>
   </si>
   <si>
+    <t>30043361</t>
+  </si>
+  <si>
+    <t>Cojinete central KH020-CBK (Cot. 14-02)</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>E002</t>
+  </si>
+  <si>
+    <t>1002691210</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>20009155</t>
+  </si>
+  <si>
+    <t>GOLILLAS M 10 A4 STAINLESS STELL WASHER</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002690021</t>
+  </si>
+  <si>
+    <t>20009279</t>
+  </si>
+  <si>
+    <t>PERNO INOX C/TUERCA 3/8" x 1.1/2"</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>30008798</t>
+  </si>
+  <si>
+    <t>SKF RODAMIENTOS SKF 23138  CCK/W33</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002690589</t>
+  </si>
+  <si>
+    <t>30008799</t>
+  </si>
+  <si>
+    <t>SKF SOPORTE RODAMIENTO SKF,  SNL-3138</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30008800</t>
+  </si>
+  <si>
+    <t>SKF MANGUITO DE FIJACION SKF  H-3138</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>30008704</t>
+  </si>
+  <si>
+    <t>SKF ANILLOS DE FIJACION FRB 10/320</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>30008661</t>
+  </si>
+  <si>
+    <t>GRAFITO SECADOR 185 X 150 X 25 MM</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>30008802</t>
+  </si>
+  <si>
+    <t>SKF SELLO DE LABERINTO TS-38</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>30008774</t>
+  </si>
+  <si>
+    <t>SKF SOPORTE RODAMIENTO SNL-3134</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>30008856</t>
+  </si>
+  <si>
+    <t>SKF MANGUITO DE FIJACION H-3134</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>30008857</t>
+  </si>
+  <si>
+    <t>SKF ANILLOS DE FIJACION FRB 10/280</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>30031092</t>
+  </si>
+  <si>
+    <t>SKF RODAMIENTOS 23134 CCK/W33</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>30008664</t>
+  </si>
+  <si>
+    <t>TYRE CHAIR  (ZAPATAS) SECADOR POS. 1</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>30008805</t>
+  </si>
+  <si>
+    <t>CONJ. EJE-PIÑON SECADOR PN C2063-RDMD-01</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002690629</t>
+  </si>
+  <si>
+    <t>SKF RODAMIENTOS SKF 23138  CCK/W33</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>SKF SOPORTE RODAMIENTO SKF,  SNL-3138</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>SKF MANGUITO DE FIJACION SKF  H-3138</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>SKF ANILLOS DE FIJACION FRB 10/320</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>GRAFITO SECADOR 185 X 150 X 25 MM</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>SKF SELLO DE LABERINTO TS-38</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>SKF SOPORTE RODAMIENTO SNL-3134</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>SKF MANGUITO DE FIJACION H-3134</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>SKF ANILLOS DE FIJACION FRB 10/280</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>SKF RODAMIENTOS 23134 CCK/W33</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>TYRE CHAIR  (ZAPATAS) SECADOR POS. 1</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>30008803</t>
+  </si>
+  <si>
+    <t>TYRES LLANTA LADO ALIMENTACION SECADOR</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>30008804</t>
+  </si>
+  <si>
+    <t>TYRES LLANTA LADO DESCARGA SECADOR</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>30008782</t>
+  </si>
+  <si>
+    <t>THRUST ROLLERS</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>30072421</t>
+  </si>
+  <si>
+    <t>PUENTE ADHERENCIA PARA HORMIGON</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002689156</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>20008355</t>
+  </si>
+  <si>
+    <t>AMARRAS PLASTICAS 4,8 X 200 MM</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002687207</t>
+  </si>
+  <si>
+    <t>30007438</t>
+  </si>
+  <si>
+    <t>GATES CORREAS TRANSM. LARGO=2120MM POS.6</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>20005498</t>
+  </si>
+  <si>
+    <t>ELECTRODO 7018  Ø3/32"</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>1002687239</t>
+  </si>
+  <si>
+    <t>20009699</t>
+  </si>
+  <si>
+    <t>TUERCAS INOX. 10 MM.</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>20014756</t>
+  </si>
+  <si>
+    <t>DISCO CUBITRON 987C 4 1/2" GRANO 36 INOX</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>20018777</t>
+  </si>
+  <si>
+    <t>TUERCA Ø 7/8" A.C. UNC</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>20021006</t>
+  </si>
+  <si>
+    <t>ESPARRAGO 3/4" X 7.1/4" A.C.</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30006495</t>
+  </si>
+  <si>
+    <t>ANILLO BUNA-70  2-309 F-8103AB</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30006715</t>
+  </si>
+  <si>
+    <t>SKF RODAMIENTO MODEL:22211EK-22211EK/C3</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30010915</t>
+  </si>
+  <si>
+    <t>FLAT R. GASKET GOROTEX Ø 1 1/2"300 LB</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>20005494</t>
+  </si>
+  <si>
+    <t>ELECTRODO 6010  Ø3/32"</t>
+  </si>
+  <si>
+    <t>20010751</t>
+  </si>
+  <si>
+    <t>FLANGE SLIP-ON A.C. 8"  150LB A-105</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>20011173</t>
+  </si>
+  <si>
+    <t>VALVULA BOLA 1/2" DE ACERO INOX. 316L</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002687240</t>
+  </si>
+  <si>
+    <t>30009365</t>
+  </si>
+  <si>
+    <t>VASO LUBRICADOR 120CC CONEXIÓN 1/4”</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30007426</t>
+  </si>
+  <si>
+    <t>CORREA TRANSM. SPB L=4250 DIN 7753</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002687241</t>
+  </si>
+  <si>
+    <t>30008779</t>
+  </si>
+  <si>
+    <t>LUBRICATING BLOCKS GRAPHITE POS. 10</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30067445</t>
+  </si>
+  <si>
+    <t>CORREA A.650MM EP400/3 4X2 31MT H-9205</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30008142</t>
+  </si>
+  <si>
+    <t>SELLO MECANICO MONORESORTE 19 MM UNIDAD</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>20004808</t>
+  </si>
+  <si>
+    <t>PINTURA SPRAY 475 CC COLOR AZUL</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002687242</t>
+  </si>
+  <si>
+    <t>20012106</t>
+  </si>
+  <si>
+    <t>AGUA OXIGENADA 50%</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30023656</t>
+  </si>
+  <si>
+    <t>SPRAY INYECTABLE POLIURETANO EP15-VF</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
     <t>20015630</t>
   </si>
   <si>
@@ -67,30 +589,9 @@
     <t>C/U</t>
   </si>
   <si>
-    <t>E002</t>
-  </si>
-  <si>
     <t>1002682089</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>20006108</t>
   </si>
   <si>
@@ -103,18 +604,6 @@
     <t>1002681353</t>
   </si>
   <si>
-    <t>20006145</t>
-  </si>
-  <si>
-    <t>AIRE COMPRIMIDO SECO LPS QB PRECISION DU</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>20006694</t>
   </si>
   <si>
@@ -124,34 +613,10 @@
     <t>C/U</t>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>20020618</t>
-  </si>
-  <si>
-    <t>CINTA AISLADORA VINYL 3M 35 VERDE</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002673990</t>
-  </si>
-  <si>
-    <t>20020513</t>
-  </si>
-  <si>
-    <t>BALIZA SOLAR MARINA LED MOD. M650H AMBAR</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>20007926</t>
-  </si>
-  <si>
-    <t>CINTA AISLADORA DE GOMA AUTOFUNDENTE 3M</t>
+    <t>20011281</t>
+  </si>
+  <si>
+    <t>NIPLE Ø 1/2" SS 316 L=4"</t>
   </si>
   <si>
     <t>C/U</t>
@@ -160,27 +625,6 @@
     <t>1002673992</t>
   </si>
   <si>
-    <t>20011281</t>
-  </si>
-  <si>
-    <t>NIPLE Ø 1/2" SS 316 L=4"</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>20017680</t>
-  </si>
-  <si>
-    <t>CANDADO BLOQUEO ROJO</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>20027476</t>
   </si>
   <si>
@@ -190,9 +634,6 @@
     <t>C/U</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>20009512</t>
   </si>
   <si>
@@ -202,10 +643,10 @@
     <t>C/U</t>
   </si>
   <si>
-    <t>20007184</t>
-  </si>
-  <si>
-    <t>JUNTA TEFLON 1.1/2 X 150 LBS.</t>
+    <t>20026818</t>
+  </si>
+  <si>
+    <t>CAÑO LANA MINERAL Ø 3/4" X 50MM L=35"</t>
   </si>
   <si>
     <t>C/U</t>
@@ -214,51 +655,6 @@
     <t>1002673993</t>
   </si>
   <si>
-    <t>20026818</t>
-  </si>
-  <si>
-    <t>CAÑO LANA MINERAL Ø 3/4" X 50MM L=35"</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>JUNTA TEFLON 1.1/2 X 150 LBS.</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30010955</t>
-  </si>
-  <si>
-    <t>SPIRAL CGI Ø2"X150LB 304/FG304/304</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30010966</t>
-  </si>
-  <si>
-    <t>EMPAQUETADURA TEFLON 1" 300# ESPESOR 1/1</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30010968</t>
-  </si>
-  <si>
-    <t>EMPAQUETADURA TEFLON 2" 300# ESPESOR 1/1</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>30007396</t>
   </si>
   <si>
@@ -271,34 +667,10 @@
     <t>1002673994</t>
   </si>
   <si>
-    <t>20004885</t>
-  </si>
-  <si>
-    <t>HIDROXIDO DE SODIO P.A. EN LENTEJAS</t>
-  </si>
-  <si>
-    <t>KG</t>
-  </si>
-  <si>
-    <t>1002673995</t>
-  </si>
-  <si>
-    <t>20070347</t>
-  </si>
-  <si>
-    <t>TUBO LED T8 1200MM 6500K 1600LM 16W FRIA</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002674971</t>
-  </si>
-  <si>
-    <t>20006695</t>
-  </si>
-  <si>
-    <t>DISCO CORTE SS Ø7" E=1/16"</t>
+    <t>20015709</t>
+  </si>
+  <si>
+    <t>FLANGE SLIP-ON  24" #150 A105 ASME B16.5</t>
   </si>
   <si>
     <t>C/U</t>
@@ -307,15 +679,6 @@
     <t>1002674973</t>
   </si>
   <si>
-    <t>20015709</t>
-  </si>
-  <si>
-    <t>FLANGE SLIP-ON  24" #150 A105 ASME B16.5</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
     <t>30010902</t>
   </si>
   <si>
@@ -388,198 +751,6 @@
     <t>C/U</t>
   </si>
   <si>
-    <t>20012425</t>
-  </si>
-  <si>
-    <t>ESLINGA PARA 4 TON., 4 MTS. LARGO</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002671085</t>
-  </si>
-  <si>
-    <t>20020665</t>
-  </si>
-  <si>
-    <t>PINTURA SPRAY 475 CC COLOR NARANJA</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30006716</t>
-  </si>
-  <si>
-    <t>SKF MANGUITO FIJACION MODEL: H-311</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30006717</t>
-  </si>
-  <si>
-    <t>SKF ANILLO FIJACI. MODEL: 2FRB 9.5/100</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30051653</t>
-  </si>
-  <si>
-    <t>MALLA SS304L 3000X1000 MESH 15X15X3MM</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>30028518</t>
-  </si>
-  <si>
-    <t>ESLINGA DOBLE TELA ANCHO 50MM LARGO 3MT</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>20012429</t>
-  </si>
-  <si>
-    <t>ESLINGA DOBLE TELA ANCHO 50MM LARGO 2,0M</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>20009196</t>
-  </si>
-  <si>
-    <t>PERNO INOX 5/8" x 3"  C/TUERCA</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>20012298</t>
-  </si>
-  <si>
-    <t>LIJA AL AGUA NR. 120 FINA</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>30007398</t>
-  </si>
-  <si>
-    <t>SKF SOPORTE RODAMIENTO SNH 516-613 POS.4</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>30017121</t>
-  </si>
-  <si>
-    <t>SKF SOPORTE DESCAN. MODEL: SNH-511-609</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>30007365</t>
-  </si>
-  <si>
-    <t>SKF RODAMIENTO 22222  CCW/33 POS.4b</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>30007363</t>
-  </si>
-  <si>
-    <t>SKF DESCANSO RODAMIE. SNH 522-619 POS.4</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>30007388</t>
-  </si>
-  <si>
-    <t>SKF RODAMIENTO 21317-E POS.6b</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>30038374</t>
-  </si>
-  <si>
-    <t>SKF RODAMIENTO 22218 CCW/33 POS.6b</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>30073790</t>
-  </si>
-  <si>
-    <t>FILTRO ABSOLUTO 20μM SUCCION PARKER</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002671112</t>
-  </si>
-  <si>
-    <t>30073791</t>
-  </si>
-  <si>
-    <t>FILTRO ABSOLUTO 5μM DESCARGA PARKER</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
     <t>30005783</t>
   </si>
   <si>
@@ -619,18 +790,6 @@
     <t>C/U</t>
   </si>
   <si>
-    <t>20004806</t>
-  </si>
-  <si>
-    <t>SPRAY ANTICORROSIVO 485ml</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002671219</t>
-  </si>
-  <si>
     <t>20027356</t>
   </si>
   <si>
@@ -649,42 +808,6 @@
     <t>05</t>
   </si>
   <si>
-    <t>30038497</t>
-  </si>
-  <si>
-    <t>ABSORVENTE VEGETAL BOLSA 5KG</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002669281</t>
-  </si>
-  <si>
-    <t>20005074</t>
-  </si>
-  <si>
-    <t>Fenolftaleina</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>1002668394</t>
-  </si>
-  <si>
-    <t>20004936</t>
-  </si>
-  <si>
-    <t>Nitrato de Potasio</t>
-  </si>
-  <si>
-    <t>20004932</t>
-  </si>
-  <si>
-    <t>Nitrato de Plata</t>
-  </si>
-  <si>
     <t>20023885</t>
   </si>
   <si>
@@ -808,30 +931,6 @@
     <t>C/U</t>
   </si>
   <si>
-    <t>20005577</t>
-  </si>
-  <si>
-    <t>SPOTCHECK REVELADOR BLANCO 16 OZ MARCA M</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002667099</t>
-  </si>
-  <si>
-    <t>30006711</t>
-  </si>
-  <si>
-    <t>SKF RODAMIENTO. MODEL: 22215-EK</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002666229</t>
-  </si>
-  <si>
     <t>20020964</t>
   </si>
   <si>
@@ -862,18 +961,6 @@
     <t>1002660930</t>
   </si>
   <si>
-    <t>20006158</t>
-  </si>
-  <si>
-    <t>PAPEL LIMPIEZA TORK MOD. 420 A 1X525MTS</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002660931</t>
-  </si>
-  <si>
     <t>30008485</t>
   </si>
   <si>
@@ -895,18 +982,6 @@
     <t>C/U</t>
   </si>
   <si>
-    <t>20040973</t>
-  </si>
-  <si>
-    <t>ANTIEMPAÑANTE SPRAY PARA VISERAS Y GAFAS</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002654974</t>
-  </si>
-  <si>
     <t>20022101</t>
   </si>
   <si>
@@ -967,39 +1042,6 @@
     <t>C/U</t>
   </si>
   <si>
-    <t>20004998</t>
-  </si>
-  <si>
-    <t>ACIDO SULFURICO P.A.</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>1002648064</t>
-  </si>
-  <si>
-    <t>30053646</t>
-  </si>
-  <si>
-    <t>PERNO SUJECION CUERPO 3/8-18X4,5 P-6864</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002637281</t>
-  </si>
-  <si>
-    <t>30039714</t>
-  </si>
-  <si>
-    <t>ORING TAPA SILICONA #36 MOD220 U1 P-6864</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
     <t>20005224</t>
   </si>
   <si>
@@ -1022,30 +1064,6 @@
   </si>
   <si>
     <t>1002631449</t>
-  </si>
-  <si>
-    <t>20013978</t>
-  </si>
-  <si>
-    <t>PEPEL INDIC. ROLLO PH1-14 C/ESC. A COLOR</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002631450</t>
-  </si>
-  <si>
-    <t>20004877</t>
-  </si>
-  <si>
-    <t>CLOROFORMO   P.A.</t>
-  </si>
-  <si>
-    <t>20020860</t>
-  </si>
-  <si>
-    <t>REACTIVO COMBITITRANT 5 KARL FICHER</t>
   </si>
   <si>
     <t>30043362</t>
@@ -1173,7 +1191,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1"/>
   </sheetPr>
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="9" customWidth="1"/>
@@ -1248,13 +1266,13 @@
         <v>16</v>
       </c>
       <c r="C2" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E2" s="4">
-        <v>46206</v>
+        <v>46217</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>18</v>
@@ -1295,13 +1313,13 @@
         <v>27</v>
       </c>
       <c r="C3" s="3">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="4">
-        <v>46205</v>
+        <v>46216</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>18</v>
@@ -1342,13 +1360,13 @@
         <v>31</v>
       </c>
       <c r="C4" s="3">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="4">
-        <v>46205</v>
+        <v>46216</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>18</v>
@@ -1389,22 +1407,22 @@
         <v>35</v>
       </c>
       <c r="C5" s="3">
-        <v>300</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E5" s="4">
-        <v>46205</v>
+        <v>46216</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>21</v>
@@ -1436,22 +1454,22 @@
         <v>39</v>
       </c>
       <c r="C6" s="3">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E6" s="4">
-        <v>46204</v>
+        <v>46216</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>21</v>
@@ -1477,28 +1495,28 @@
     </row>
     <row r="7" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="3">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="3">
-        <v>3</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="4">
+        <v>46216</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E7" s="4">
-        <v>46204</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>21</v>
@@ -1530,22 +1548,22 @@
         <v>46</v>
       </c>
       <c r="C8" s="3">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E8" s="4">
-        <v>46204</v>
+        <v>46216</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>21</v>
@@ -1577,22 +1595,22 @@
         <v>50</v>
       </c>
       <c r="C9" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E9" s="4">
-        <v>46204</v>
+        <v>46216</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>21</v>
@@ -1618,28 +1636,28 @@
     </row>
     <row r="10" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" s="3">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" s="4">
-        <v>46204</v>
+        <v>46216</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>21</v>
@@ -1665,28 +1683,28 @@
     </row>
     <row r="11" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" s="4">
-        <v>46204</v>
+        <v>46216</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>21</v>
@@ -1712,28 +1730,28 @@
     </row>
     <row r="12" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A12" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="3">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E12" s="4">
-        <v>46204</v>
+        <v>46216</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>21</v>
@@ -1759,28 +1777,28 @@
     </row>
     <row r="13" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" s="3">
         <v>2</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E13" s="4">
-        <v>46204</v>
+        <v>46216</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>21</v>
@@ -1806,28 +1824,28 @@
     </row>
     <row r="14" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A14" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C14" s="3">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E14" s="4">
-        <v>46204</v>
+        <v>46216</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>21</v>
@@ -1853,28 +1871,28 @@
     </row>
     <row r="15" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A15" s="2" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C15" s="3">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E15" s="4">
-        <v>46204</v>
+        <v>46216</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>21</v>
@@ -1900,28 +1918,28 @@
     </row>
     <row r="16" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A16" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C16" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E16" s="4">
-        <v>46204</v>
+        <v>46216</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>21</v>
@@ -1947,28 +1965,28 @@
     </row>
     <row r="17" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A17" s="2" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C17" s="3">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E17" s="4">
-        <v>46204</v>
+        <v>46216</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>21</v>
@@ -1994,28 +2012,28 @@
     </row>
     <row r="18" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A18" s="2" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C18" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="4">
+        <v>46216</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="4">
-        <v>46204</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>21</v>
@@ -2041,28 +2059,28 @@
     </row>
     <row r="19" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A19" s="2" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C19" s="3">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E19" s="4">
-        <v>46204</v>
+        <v>46216</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>21</v>
@@ -2088,28 +2106,28 @@
     </row>
     <row r="20" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A20" s="2" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="5">
-        <v>10.000</v>
+      <c r="C20" s="3">
+        <v>32</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>88</v>
       </c>
       <c r="E20" s="4">
-        <v>46204</v>
+        <v>46216</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>21</v>
@@ -2135,28 +2153,28 @@
     </row>
     <row r="21" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="3">
+        <v>16</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="3">
-        <v>400</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="E21" s="4">
-        <v>46197</v>
+        <v>46216</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>21</v>
@@ -2182,28 +2200,28 @@
     </row>
     <row r="22" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A22" s="2" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C22" s="3">
-        <v>250</v>
+        <v>16</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E22" s="4">
-        <v>46197</v>
+        <v>46216</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>21</v>
@@ -2229,28 +2247,28 @@
     </row>
     <row r="23" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A23" s="2" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C23" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E23" s="4">
-        <v>46197</v>
+        <v>46216</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>21</v>
@@ -2276,28 +2294,28 @@
     </row>
     <row r="24" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A24" s="2" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C24" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E24" s="4">
-        <v>46197</v>
+        <v>46216</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>21</v>
@@ -2323,28 +2341,28 @@
     </row>
     <row r="25" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A25" s="2" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C25" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E25" s="4">
-        <v>46197</v>
+        <v>46216</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>21</v>
@@ -2370,28 +2388,28 @@
     </row>
     <row r="26" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A26" s="2" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C26" s="3">
+        <v>2</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" s="4">
+        <v>46216</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E26" s="4">
-        <v>46197</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="H26" s="2" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>21</v>
@@ -2417,28 +2435,28 @@
     </row>
     <row r="27" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A27" s="2" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="3">
         <v>112</v>
       </c>
-      <c r="C27" s="3">
-        <v>2</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E27" s="4">
-        <v>46196</v>
+        <v>46216</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>21</v>
@@ -2464,28 +2482,28 @@
     </row>
     <row r="28" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A28" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C28" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E28" s="4">
-        <v>46191</v>
+        <v>46216</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>21</v>
@@ -2511,28 +2529,28 @@
     </row>
     <row r="29" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A29" s="2" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C29" s="3">
         <v>2</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E29" s="4">
-        <v>46191</v>
+        <v>46216</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>21</v>
@@ -2558,28 +2576,28 @@
     </row>
     <row r="30" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A30" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C30" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E30" s="4">
-        <v>46191</v>
+        <v>46216</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>21</v>
@@ -2605,28 +2623,28 @@
     </row>
     <row r="31" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A31" s="2" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C31" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E31" s="4">
-        <v>46191</v>
+        <v>46213</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>21</v>
@@ -2641,10 +2659,10 @@
         <v>23</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>25</v>
@@ -2652,28 +2670,28 @@
     </row>
     <row r="32" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A32" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C32" s="3">
-        <v>4</v>
+        <v>3000</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E32" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>21</v>
@@ -2699,28 +2717,28 @@
     </row>
     <row r="33" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A33" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C33" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E33" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>21</v>
@@ -2746,28 +2764,28 @@
     </row>
     <row r="34" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A34" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C34" s="3">
+        <v>130</v>
+      </c>
+      <c r="C34" s="5">
+        <v>50.000</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E34" s="4">
+        <v>46211</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E34" s="4">
-        <v>46191</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>21</v>
@@ -2793,28 +2811,28 @@
     </row>
     <row r="35" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A35" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C35" s="3">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E35" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>141</v>
+        <v>33</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>21</v>
@@ -2840,28 +2858,28 @@
     </row>
     <row r="36" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A36" s="2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C36" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E36" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>21</v>
@@ -2887,28 +2905,28 @@
     </row>
     <row r="37" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A37" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C37" s="3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E37" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>21</v>
@@ -2934,28 +2952,28 @@
     </row>
     <row r="38" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A38" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C38" s="3">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E38" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>21</v>
@@ -2981,28 +2999,28 @@
     </row>
     <row r="39" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A39" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C39" s="3">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E39" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>21</v>
@@ -3028,28 +3046,28 @@
     </row>
     <row r="40" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A40" s="2" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C40" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E40" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>21</v>
@@ -3075,28 +3093,28 @@
     </row>
     <row r="41" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A41" s="2" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C41" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="E41" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>21</v>
@@ -3122,28 +3140,28 @@
     </row>
     <row r="42" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A42" s="2" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C42" s="3">
-        <v>2</v>
+        <v>155</v>
+      </c>
+      <c r="C42" s="5">
+        <v>20.000</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="E42" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>21</v>
@@ -3169,28 +3187,28 @@
     </row>
     <row r="43" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A43" s="2" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="C43" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="E43" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>21</v>
@@ -3216,28 +3234,28 @@
     </row>
     <row r="44" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A44" s="2" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C44" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="E44" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>177</v>
+        <v>20</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>21</v>
@@ -3263,28 +3281,28 @@
     </row>
     <row r="45" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A45" s="2" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="C45" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E45" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>181</v>
+        <v>52</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>21</v>
@@ -3310,25 +3328,25 @@
     </row>
     <row r="46" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A46" s="2" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C46" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="E46" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>20</v>
@@ -3357,25 +3375,25 @@
     </row>
     <row r="47" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A47" s="2" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="C47" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="E47" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>33</v>
@@ -3404,28 +3422,28 @@
     </row>
     <row r="48" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A48" s="2" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="C48" s="3">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="E48" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>21</v>
@@ -3451,28 +3469,28 @@
     </row>
     <row r="49" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A49" s="2" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="C49" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="E49" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>21</v>
@@ -3498,28 +3516,28 @@
     </row>
     <row r="50" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A50" s="2" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="C50" s="3">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="E50" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>21</v>
@@ -3545,28 +3563,28 @@
     </row>
     <row r="51" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A51" s="2" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="C51" s="3">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="E51" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>21</v>
@@ -3592,28 +3610,28 @@
     </row>
     <row r="52" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A52" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="C52" s="3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E52" s="4">
-        <v>46191</v>
+        <v>46211</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>21</v>
@@ -3639,28 +3657,28 @@
     </row>
     <row r="53" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A53" s="2" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="C53" s="3">
         <v>20</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="E53" s="4">
-        <v>46191</v>
+        <v>46206</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>21</v>
@@ -3675,10 +3693,10 @@
         <v>23</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>211</v>
+        <v>24</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>25</v>
@@ -3686,25 +3704,25 @@
     </row>
     <row r="54" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A54" s="2" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="C54" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="E54" s="4">
-        <v>46189</v>
+        <v>46205</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>20</v>
@@ -3733,28 +3751,28 @@
     </row>
     <row r="55" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A55" s="2" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="C55" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="E55" s="4">
-        <v>46188</v>
+        <v>46205</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>21</v>
@@ -3780,25 +3798,25 @@
     </row>
     <row r="56" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A56" s="2" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C56" s="5">
-        <v>1.000</v>
+        <v>201</v>
+      </c>
+      <c r="C56" s="3">
+        <v>20</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>88</v>
+        <v>202</v>
       </c>
       <c r="E56" s="4">
-        <v>46188</v>
+        <v>46204</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>33</v>
@@ -3827,28 +3845,28 @@
     </row>
     <row r="57" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A57" s="2" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="C57" s="3">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="E57" s="4">
-        <v>46188</v>
+        <v>46204</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>21</v>
@@ -3874,28 +3892,28 @@
     </row>
     <row r="58" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A58" s="2" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="C58" s="3">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="E58" s="4">
-        <v>46185</v>
+        <v>46204</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>21</v>
@@ -3921,28 +3939,28 @@
     </row>
     <row r="59" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A59" s="2" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="C59" s="3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="E59" s="4">
-        <v>46185</v>
+        <v>46204</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>21</v>
@@ -3968,28 +3986,28 @@
     </row>
     <row r="60" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A60" s="2" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="C60" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="E60" s="4">
-        <v>46185</v>
+        <v>46204</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>21</v>
@@ -4015,28 +4033,28 @@
     </row>
     <row r="61" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A61" s="2" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C61" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="E61" s="4">
-        <v>46185</v>
+        <v>46197</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>21</v>
@@ -4062,28 +4080,28 @@
     </row>
     <row r="62" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A62" s="2" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="C62" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="E62" s="4">
-        <v>46185</v>
+        <v>46197</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>21</v>
@@ -4109,28 +4127,28 @@
     </row>
     <row r="63" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A63" s="2" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="C63" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E63" s="4">
-        <v>46185</v>
+        <v>46197</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>141</v>
+        <v>33</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>21</v>
@@ -4156,28 +4174,28 @@
     </row>
     <row r="64" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A64" s="2" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="C64" s="3">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="E64" s="4">
-        <v>46185</v>
+        <v>46197</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>21</v>
@@ -4203,28 +4221,28 @@
     </row>
     <row r="65" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A65" s="2" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="C65" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="E65" s="4">
-        <v>46185</v>
+        <v>46196</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>21</v>
@@ -4250,28 +4268,28 @@
     </row>
     <row r="66" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A66" s="2" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="C66" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="E66" s="4">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>21</v>
@@ -4297,28 +4315,28 @@
     </row>
     <row r="67" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A67" s="2" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="C67" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="E67" s="4">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>21</v>
@@ -4344,28 +4362,28 @@
     </row>
     <row r="68" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A68" s="2" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="C68" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="E68" s="4">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>21</v>
@@ -4391,19 +4409,19 @@
     </row>
     <row r="69" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A69" s="2" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="C69" s="3">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="E69" s="4">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>18</v>
@@ -4412,7 +4430,7 @@
         <v>249</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>21</v>
@@ -4438,19 +4456,19 @@
     </row>
     <row r="70" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A70" s="2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="C70" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="E70" s="4">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>18</v>
@@ -4459,7 +4477,7 @@
         <v>249</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>153</v>
+        <v>33</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>21</v>
@@ -4485,28 +4503,28 @@
     </row>
     <row r="71" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A71" s="2" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C71" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="E71" s="4">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>21</v>
@@ -4532,28 +4550,28 @@
     </row>
     <row r="72" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A72" s="2" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="C72" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="E72" s="4">
-        <v>46184</v>
+        <v>46191</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>21</v>
@@ -4568,10 +4586,10 @@
         <v>23</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>211</v>
+        <v>24</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>25</v>
@@ -4579,25 +4597,25 @@
     </row>
     <row r="73" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A73" s="2" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="C73" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="E73" s="4">
-        <v>46182</v>
+        <v>46191</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>33</v>
@@ -4615,10 +4633,10 @@
         <v>23</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>21</v>
+        <v>263</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>24</v>
+        <v>264</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>25</v>
@@ -4626,28 +4644,28 @@
     </row>
     <row r="74" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A74" s="2" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C74" s="3">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="E74" s="4">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>21</v>
@@ -4673,28 +4691,28 @@
     </row>
     <row r="75" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A75" s="2" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C75" s="5">
-        <v>108.000</v>
+        <v>270</v>
+      </c>
+      <c r="C75" s="3">
+        <v>40</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>88</v>
+        <v>271</v>
       </c>
       <c r="E75" s="4">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>21</v>
@@ -4720,28 +4738,28 @@
     </row>
     <row r="76" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A76" s="2" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="C76" s="3">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E76" s="4">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>21</v>
@@ -4767,28 +4785,28 @@
     </row>
     <row r="77" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A77" s="2" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C77" s="3">
         <v>4</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="E77" s="4">
-        <v>46171</v>
+        <v>46185</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>21</v>
@@ -4814,28 +4832,28 @@
     </row>
     <row r="78" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A78" s="2" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="C78" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="E78" s="4">
-        <v>46171</v>
+        <v>46185</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>21</v>
@@ -4861,28 +4879,28 @@
     </row>
     <row r="79" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A79" s="2" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="C79" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="E79" s="4">
-        <v>46171</v>
+        <v>46185</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>21</v>
@@ -4908,28 +4926,28 @@
     </row>
     <row r="80" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A80" s="2" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="C80" s="3">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="E80" s="4">
-        <v>46162</v>
+        <v>46185</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>21</v>
@@ -4955,28 +4973,28 @@
     </row>
     <row r="81" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A81" s="2" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="C81" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="E81" s="4">
-        <v>46162</v>
+        <v>46185</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>21</v>
@@ -5002,28 +5020,28 @@
     </row>
     <row r="82" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A82" s="2" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="C82" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="E82" s="4">
-        <v>46162</v>
+        <v>46185</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>21</v>
@@ -5049,28 +5067,28 @@
     </row>
     <row r="83" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A83" s="2" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="C83" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="E83" s="4">
-        <v>46162</v>
+        <v>46185</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>21</v>
@@ -5096,28 +5114,28 @@
     </row>
     <row r="84" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A84" s="2" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="C84" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="E84" s="4">
-        <v>46162</v>
+        <v>46185</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>21</v>
@@ -5143,28 +5161,28 @@
     </row>
     <row r="85" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A85" s="2" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="C85" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="E85" s="4">
-        <v>46162</v>
+        <v>46185</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>21</v>
@@ -5190,28 +5208,28 @@
     </row>
     <row r="86" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A86" s="2" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="C86" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="E86" s="4">
-        <v>46162</v>
+        <v>46185</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>321</v>
+        <v>290</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>21</v>
@@ -5237,28 +5255,28 @@
     </row>
     <row r="87" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A87" s="2" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="C87" s="3">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="E87" s="4">
-        <v>46148</v>
+        <v>46182</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>21</v>
@@ -5284,28 +5302,28 @@
     </row>
     <row r="88" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A88" s="2" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="C88" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="E88" s="4">
-        <v>46148</v>
+        <v>46182</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>21</v>
@@ -5331,28 +5349,28 @@
     </row>
     <row r="89" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A89" s="2" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C89" s="3">
-        <v>2</v>
+        <v>314</v>
+      </c>
+      <c r="C89" s="5">
+        <v>108.000</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>331</v>
+        <v>131</v>
       </c>
       <c r="E89" s="4">
-        <v>46148</v>
+        <v>46178</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>21</v>
@@ -5378,28 +5396,28 @@
     </row>
     <row r="90" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A90" s="2" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="C90" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="E90" s="4">
-        <v>46140</v>
+        <v>46171</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>21</v>
@@ -5425,28 +5443,28 @@
     </row>
     <row r="91" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A91" s="2" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="C91" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="E91" s="4">
-        <v>46140</v>
+        <v>46171</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>21</v>
@@ -5472,28 +5490,28 @@
     </row>
     <row r="92" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A92" s="2" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="C92" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E92" s="4">
-        <v>46140</v>
+        <v>46162</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>21</v>
@@ -5519,28 +5537,28 @@
     </row>
     <row r="93" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A93" s="2" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="C93" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E93" s="4">
-        <v>46140</v>
+        <v>46162</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>21</v>
@@ -5566,48 +5584,330 @@
     </row>
     <row r="94" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A94" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C94" s="3">
+        <v>4</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E94" s="4">
+        <v>46162</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K94" s="4">
+        <v/>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O94" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" outlineLevel="0" collapsed="0" hidden="0">
+      <c r="A95" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C95" s="3">
+        <v>5</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E95" s="4">
+        <v>46162</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K95" s="4">
+        <v/>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O95" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" outlineLevel="0" collapsed="0" hidden="0">
+      <c r="A96" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C96" s="3">
+        <v>4</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E96" s="4">
+        <v>46162</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K96" s="4">
+        <v/>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M96" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O96" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" outlineLevel="0" collapsed="0" hidden="0">
+      <c r="A97" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C97" s="3">
+        <v>8</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E97" s="4">
+        <v>46162</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K97" s="4">
+        <v/>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98" outlineLevel="0" collapsed="0" hidden="0">
+      <c r="A98" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C98" s="3">
+        <v>2</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="E98" s="4">
+        <v>46148</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C94" s="3">
+      <c r="H98" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K98" s="4">
+        <v/>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O98" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" outlineLevel="0" collapsed="0" hidden="0">
+      <c r="A99" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C99" s="3">
         <v>3</v>
       </c>
-      <c r="D94" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E94" s="4">
+      <c r="D99" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E99" s="4">
+        <v>46140</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K99" s="4">
+        <v/>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100" outlineLevel="0" collapsed="0" hidden="0">
+      <c r="A100" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C100" s="3">
+        <v>3</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E100" s="4">
         <v>46031</v>
       </c>
-      <c r="F94" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J94" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K94" s="4">
-        <v/>
-      </c>
-      <c r="L94" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M94" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N94" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O94" s="2" t="s">
+      <c r="F100" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K100" s="4">
+        <v/>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M100" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N100" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O100" s="2" t="s">
         <v>25</v>
       </c>
     </row>

--- a/mrp-panel-enaex/mrp-panel-enaex/data/ME5A/ME5A.XLSX
+++ b/mrp-panel-enaex/mrp-panel-enaex/data/ME5A/ME5A.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="349">
   <si>
     <t>Material</t>
   </si>
@@ -58,10 +58,10 @@
     <t>Status tratamiento</t>
   </si>
   <si>
-    <t>30043361</t>
-  </si>
-  <si>
-    <t>Cojinete central KH020-CBK (Cot. 14-02)</t>
+    <t>20015630</t>
+  </si>
+  <si>
+    <t>VALVULA GATE Ø 1" 800LB SW A.C.</t>
   </si>
   <si>
     <t>C/U</t>
@@ -70,7 +70,7 @@
     <t>E002</t>
   </si>
   <si>
-    <t>1002691210</t>
+    <t>1002682089</t>
   </si>
   <si>
     <t>10</t>
@@ -91,22 +91,22 @@
     <t>N</t>
   </si>
   <si>
-    <t>20009155</t>
-  </si>
-  <si>
-    <t>GOLILLAS M 10 A4 STAINLESS STELL WASHER</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002690021</t>
-  </si>
-  <si>
-    <t>20009279</t>
-  </si>
-  <si>
-    <t>PERNO INOX C/TUERCA 3/8" x 1.1/2"</t>
+    <t>20006108</t>
+  </si>
+  <si>
+    <t>ESCOBILLA DE BRONCE CON MANGO</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002681353</t>
+  </si>
+  <si>
+    <t>20006145</t>
+  </si>
+  <si>
+    <t>AIRE COMPRIMIDO SECO LPS QB PRECISION DU</t>
   </si>
   <si>
     <t>C/U</t>
@@ -115,31 +115,64 @@
     <t>20</t>
   </si>
   <si>
-    <t>30008798</t>
-  </si>
-  <si>
-    <t>SKF RODAMIENTOS SKF 23138  CCK/W33</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002690589</t>
-  </si>
-  <si>
-    <t>30008799</t>
-  </si>
-  <si>
-    <t>SKF SOPORTE RODAMIENTO SKF,  SNL-3138</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30008800</t>
-  </si>
-  <si>
-    <t>SKF MANGUITO DE FIJACION SKF  H-3138</t>
+    <t>20006694</t>
+  </si>
+  <si>
+    <t>DISCO CORTE SS Ø4 1/2" E=3/64"</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>20020618</t>
+  </si>
+  <si>
+    <t>CINTA AISLADORA VINYL 3M 35 VERDE</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002673990</t>
+  </si>
+  <si>
+    <t>20020513</t>
+  </si>
+  <si>
+    <t>BALIZA SOLAR MARINA LED MOD. M650H AMBAR</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>20007926</t>
+  </si>
+  <si>
+    <t>CINTA AISLADORA DE GOMA AUTOFUNDENTE 3M</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002673992</t>
+  </si>
+  <si>
+    <t>20011281</t>
+  </si>
+  <si>
+    <t>NIPLE Ø 1/2" SS 316 L=4"</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>20017680</t>
+  </si>
+  <si>
+    <t>CANDADO BLOQUEO ROJO</t>
   </si>
   <si>
     <t>C/U</t>
@@ -148,10 +181,10 @@
     <t>30</t>
   </si>
   <si>
-    <t>30008704</t>
-  </si>
-  <si>
-    <t>SKF ANILLOS DE FIJACION FRB 10/320</t>
+    <t>20027476</t>
+  </si>
+  <si>
+    <t>PERNO ANCLAJE INOX. 1/2 X 5.1/2 Y TUERCA</t>
   </si>
   <si>
     <t>C/U</t>
@@ -160,22 +193,64 @@
     <t>40</t>
   </si>
   <si>
-    <t>30008661</t>
-  </si>
-  <si>
-    <t>GRAFITO SECADOR 185 X 150 X 25 MM</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>30008802</t>
-  </si>
-  <si>
-    <t>SKF SELLO DE LABERINTO TS-38</t>
+    <t>20009512</t>
+  </si>
+  <si>
+    <t>PERNO Ø5/8" L=2" SS316 C/TUERCA</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>20007184</t>
+  </si>
+  <si>
+    <t>JUNTA TEFLON 1.1/2 X 150 LBS.</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002673993</t>
+  </si>
+  <si>
+    <t>20026818</t>
+  </si>
+  <si>
+    <t>CAÑO LANA MINERAL Ø 3/4" X 50MM L=35"</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>JUNTA TEFLON 1.1/2 X 150 LBS.</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30010955</t>
+  </si>
+  <si>
+    <t>SPIRAL CGI Ø2"X150LB 304/FG304/304</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30010966</t>
+  </si>
+  <si>
+    <t>EMPAQUETADURA TEFLON 1" 300# ESPESOR 1/1</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30010968</t>
+  </si>
+  <si>
+    <t>EMPAQUETADURA TEFLON 2" 300# ESPESOR 1/1</t>
   </si>
   <si>
     <t>C/U</t>
@@ -184,10 +259,178 @@
     <t>60</t>
   </si>
   <si>
-    <t>30008774</t>
-  </si>
-  <si>
-    <t>SKF SOPORTE RODAMIENTO SNL-3134</t>
+    <t>30007396</t>
+  </si>
+  <si>
+    <t>IMPELLER DIAMETRO 1405 CCW POS.1</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002673994</t>
+  </si>
+  <si>
+    <t>20004885</t>
+  </si>
+  <si>
+    <t>HIDROXIDO DE SODIO P.A. EN LENTEJAS</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>1002673995</t>
+  </si>
+  <si>
+    <t>20070347</t>
+  </si>
+  <si>
+    <t>TUBO LED T8 1200MM 6500K 1600LM 16W FRIA</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002674971</t>
+  </si>
+  <si>
+    <t>20006695</t>
+  </si>
+  <si>
+    <t>DISCO CORTE SS Ø7" E=1/16"</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002674973</t>
+  </si>
+  <si>
+    <t>20015709</t>
+  </si>
+  <si>
+    <t>FLANGE SLIP-ON  24" #150 A105 ASME B16.5</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30010902</t>
+  </si>
+  <si>
+    <t>EMPAQUETADURA GOROTEX 2"X150LB</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002674974</t>
+  </si>
+  <si>
+    <t>30051089</t>
+  </si>
+  <si>
+    <t>ANILLO SEGUR NL100 316 NETCHZ</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>20024067</t>
+  </si>
+  <si>
+    <t>FILTRO CARTUCHO VEOPP 40X5µ</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30007387</t>
+  </si>
+  <si>
+    <t>SKF OBTURADOR DOBLE TSNA  317-G POS.6a</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002674290</t>
+  </si>
+  <si>
+    <t>30007331</t>
+  </si>
+  <si>
+    <t>POLEA MOTOR DIA. 250MM 3 CANALES</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002671083</t>
+  </si>
+  <si>
+    <t>30007332</t>
+  </si>
+  <si>
+    <t>POLEA VENTILADOR DIA.160MM 3 CANALES</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30023347</t>
+  </si>
+  <si>
+    <t>TRANSMION ACOPLAMIE. 125 64 ShD-F  POS.7</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>20012425</t>
+  </si>
+  <si>
+    <t>ESLINGA PARA 4 TON., 4 MTS. LARGO</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002671085</t>
+  </si>
+  <si>
+    <t>20020665</t>
+  </si>
+  <si>
+    <t>PINTURA SPRAY 475 CC COLOR NARANJA</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30006716</t>
+  </si>
+  <si>
+    <t>SKF MANGUITO FIJACION MODEL: H-311</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30006717</t>
+  </si>
+  <si>
+    <t>SKF ANILLO FIJACI. MODEL: 2FRB 9.5/100</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>30051653</t>
+  </si>
+  <si>
+    <t>MALLA SS304L 3000X1000 MESH 15X15X3MM</t>
   </si>
   <si>
     <t>C/U</t>
@@ -196,10 +439,10 @@
     <t>70</t>
   </si>
   <si>
-    <t>30008856</t>
-  </si>
-  <si>
-    <t>SKF MANGUITO DE FIJACION H-3134</t>
+    <t>30028518</t>
+  </si>
+  <si>
+    <t>ESLINGA DOBLE TELA ANCHO 50MM LARGO 3MT</t>
   </si>
   <si>
     <t>C/U</t>
@@ -208,10 +451,10 @@
     <t>80</t>
   </si>
   <si>
-    <t>30008857</t>
-  </si>
-  <si>
-    <t>SKF ANILLOS DE FIJACION FRB 10/280</t>
+    <t>20012429</t>
+  </si>
+  <si>
+    <t>ESLINGA DOBLE TELA ANCHO 50MM LARGO 2,0M</t>
   </si>
   <si>
     <t>C/U</t>
@@ -220,10 +463,10 @@
     <t>90</t>
   </si>
   <si>
-    <t>30031092</t>
-  </si>
-  <si>
-    <t>SKF RODAMIENTOS 23134 CCK/W33</t>
+    <t>20009196</t>
+  </si>
+  <si>
+    <t>PERNO INOX 5/8" x 3"  C/TUERCA</t>
   </si>
   <si>
     <t>C/U</t>
@@ -232,10 +475,10 @@
     <t>100</t>
   </si>
   <si>
-    <t>30008664</t>
-  </si>
-  <si>
-    <t>TYRE CHAIR  (ZAPATAS) SECADOR POS. 1</t>
+    <t>20012298</t>
+  </si>
+  <si>
+    <t>LIJA AL AGUA NR. 120 FINA</t>
   </si>
   <si>
     <t>C/U</t>
@@ -244,79 +487,10 @@
     <t>110</t>
   </si>
   <si>
-    <t>30008805</t>
-  </si>
-  <si>
-    <t>CONJ. EJE-PIÑON SECADOR PN C2063-RDMD-01</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002690629</t>
-  </si>
-  <si>
-    <t>SKF RODAMIENTOS SKF 23138  CCK/W33</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>SKF SOPORTE RODAMIENTO SKF,  SNL-3138</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>SKF MANGUITO DE FIJACION SKF  H-3138</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>SKF ANILLOS DE FIJACION FRB 10/320</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>GRAFITO SECADOR 185 X 150 X 25 MM</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>SKF SELLO DE LABERINTO TS-38</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>SKF SOPORTE RODAMIENTO SNL-3134</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>SKF MANGUITO DE FIJACION H-3134</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>SKF ANILLOS DE FIJACION FRB 10/280</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>SKF RODAMIENTOS 23134 CCK/W33</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>TYRE CHAIR  (ZAPATAS) SECADOR POS. 1</t>
+    <t>30007398</t>
+  </si>
+  <si>
+    <t>SKF SOPORTE RODAMIENTO SNH 516-613 POS.4</t>
   </si>
   <si>
     <t>C/U</t>
@@ -325,10 +499,10 @@
     <t>120</t>
   </si>
   <si>
-    <t>30008803</t>
-  </si>
-  <si>
-    <t>TYRES LLANTA LADO ALIMENTACION SECADOR</t>
+    <t>30017121</t>
+  </si>
+  <si>
+    <t>SKF SOPORTE DESCAN. MODEL: SNH-511-609</t>
   </si>
   <si>
     <t>C/U</t>
@@ -337,10 +511,10 @@
     <t>130</t>
   </si>
   <si>
-    <t>30008804</t>
-  </si>
-  <si>
-    <t>TYRES LLANTA LADO DESCARGA SECADOR</t>
+    <t>30007365</t>
+  </si>
+  <si>
+    <t>SKF RODAMIENTO 22222  CCW/33 POS.4b</t>
   </si>
   <si>
     <t>C/U</t>
@@ -349,10 +523,10 @@
     <t>140</t>
   </si>
   <si>
-    <t>30008782</t>
-  </si>
-  <si>
-    <t>THRUST ROLLERS</t>
+    <t>30007363</t>
+  </si>
+  <si>
+    <t>SKF DESCANSO RODAMIE. SNH 522-619 POS.4</t>
   </si>
   <si>
     <t>C/U</t>
@@ -361,391 +535,46 @@
     <t>150</t>
   </si>
   <si>
-    <t>30072421</t>
-  </si>
-  <si>
-    <t>PUENTE ADHERENCIA PARA HORMIGON</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002689156</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>20008355</t>
-  </si>
-  <si>
-    <t>AMARRAS PLASTICAS 4,8 X 200 MM</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002687207</t>
-  </si>
-  <si>
-    <t>30007438</t>
-  </si>
-  <si>
-    <t>GATES CORREAS TRANSM. LARGO=2120MM POS.6</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>20005498</t>
-  </si>
-  <si>
-    <t>ELECTRODO 7018  Ø3/32"</t>
-  </si>
-  <si>
-    <t>KG</t>
-  </si>
-  <si>
-    <t>1002687239</t>
-  </si>
-  <si>
-    <t>20009699</t>
-  </si>
-  <si>
-    <t>TUERCAS INOX. 10 MM.</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>20014756</t>
-  </si>
-  <si>
-    <t>DISCO CUBITRON 987C 4 1/2" GRANO 36 INOX</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>20018777</t>
-  </si>
-  <si>
-    <t>TUERCA Ø 7/8" A.C. UNC</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>20021006</t>
-  </si>
-  <si>
-    <t>ESPARRAGO 3/4" X 7.1/4" A.C.</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30006495</t>
-  </si>
-  <si>
-    <t>ANILLO BUNA-70  2-309 F-8103AB</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30006715</t>
-  </si>
-  <si>
-    <t>SKF RODAMIENTO MODEL:22211EK-22211EK/C3</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30010915</t>
-  </si>
-  <si>
-    <t>FLAT R. GASKET GOROTEX Ø 1 1/2"300 LB</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>20005494</t>
-  </si>
-  <si>
-    <t>ELECTRODO 6010  Ø3/32"</t>
-  </si>
-  <si>
-    <t>20010751</t>
-  </si>
-  <si>
-    <t>FLANGE SLIP-ON A.C. 8"  150LB A-105</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>20011173</t>
-  </si>
-  <si>
-    <t>VALVULA BOLA 1/2" DE ACERO INOX. 316L</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002687240</t>
-  </si>
-  <si>
-    <t>30009365</t>
-  </si>
-  <si>
-    <t>VASO LUBRICADOR 120CC CONEXIÓN 1/4”</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30007426</t>
-  </si>
-  <si>
-    <t>CORREA TRANSM. SPB L=4250 DIN 7753</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002687241</t>
-  </si>
-  <si>
-    <t>30008779</t>
-  </si>
-  <si>
-    <t>LUBRICATING BLOCKS GRAPHITE POS. 10</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30067445</t>
-  </si>
-  <si>
-    <t>CORREA A.650MM EP400/3 4X2 31MT H-9205</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30008142</t>
-  </si>
-  <si>
-    <t>SELLO MECANICO MONORESORTE 19 MM UNIDAD</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>20004808</t>
-  </si>
-  <si>
-    <t>PINTURA SPRAY 475 CC COLOR AZUL</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002687242</t>
-  </si>
-  <si>
-    <t>20012106</t>
-  </si>
-  <si>
-    <t>AGUA OXIGENADA 50%</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30023656</t>
-  </si>
-  <si>
-    <t>SPRAY INYECTABLE POLIURETANO EP15-VF</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>20015630</t>
-  </si>
-  <si>
-    <t>VALVULA GATE Ø 1" 800LB SW A.C.</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002682089</t>
-  </si>
-  <si>
-    <t>20006108</t>
-  </si>
-  <si>
-    <t>ESCOBILLA DE BRONCE CON MANGO</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002681353</t>
-  </si>
-  <si>
-    <t>20006694</t>
-  </si>
-  <si>
-    <t>DISCO CORTE SS Ø4 1/2" E=3/64"</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>20011281</t>
-  </si>
-  <si>
-    <t>NIPLE Ø 1/2" SS 316 L=4"</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002673992</t>
-  </si>
-  <si>
-    <t>20027476</t>
-  </si>
-  <si>
-    <t>PERNO ANCLAJE INOX. 1/2 X 5.1/2 Y TUERCA</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>20009512</t>
-  </si>
-  <si>
-    <t>PERNO Ø5/8" L=2" SS316 C/TUERCA</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>20026818</t>
-  </si>
-  <si>
-    <t>CAÑO LANA MINERAL Ø 3/4" X 50MM L=35"</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002673993</t>
-  </si>
-  <si>
-    <t>30007396</t>
-  </si>
-  <si>
-    <t>IMPELLER DIAMETRO 1405 CCW POS.1</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002673994</t>
-  </si>
-  <si>
-    <t>20015709</t>
-  </si>
-  <si>
-    <t>FLANGE SLIP-ON  24" #150 A105 ASME B16.5</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002674973</t>
-  </si>
-  <si>
-    <t>30010902</t>
-  </si>
-  <si>
-    <t>EMPAQUETADURA GOROTEX 2"X150LB</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002674974</t>
-  </si>
-  <si>
-    <t>30051089</t>
-  </si>
-  <si>
-    <t>ANILLO SEGUR NL100 316 NETCHZ</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>20024067</t>
-  </si>
-  <si>
-    <t>FILTRO CARTUCHO VEOPP 40X5µ</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30007387</t>
-  </si>
-  <si>
-    <t>SKF OBTURADOR DOBLE TSNA  317-G POS.6a</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002674290</t>
-  </si>
-  <si>
-    <t>30007331</t>
-  </si>
-  <si>
-    <t>POLEA MOTOR DIA. 250MM 3 CANALES</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>1002671083</t>
-  </si>
-  <si>
-    <t>30007332</t>
-  </si>
-  <si>
-    <t>POLEA VENTILADOR DIA.160MM 3 CANALES</t>
-  </si>
-  <si>
-    <t>C/U</t>
-  </si>
-  <si>
-    <t>30023347</t>
-  </si>
-  <si>
-    <t>TRANSMION ACOPLAMIE. 125 64 ShD-F  POS.7</t>
+    <t>30007388</t>
+  </si>
+  <si>
+    <t>SKF RODAMIENTO 21317-E POS.6b</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>30038374</t>
+  </si>
+  <si>
+    <t>SKF RODAMIENTO 22218 CCW/33 POS.6b</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>30073790</t>
+  </si>
+  <si>
+    <t>FILTRO ABSOLUTO 20μM SUCCION PARKER</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002671112</t>
+  </si>
+  <si>
+    <t>30073791</t>
+  </si>
+  <si>
+    <t>FILTRO ABSOLUTO 5μM DESCARGA PARKER</t>
   </si>
   <si>
     <t>C/U</t>
@@ -790,6 +619,18 @@
     <t>C/U</t>
   </si>
   <si>
+    <t>20004806</t>
+  </si>
+  <si>
+    <t>SPRAY ANTICORROSIVO 485ml</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002671219</t>
+  </si>
+  <si>
     <t>20027356</t>
   </si>
   <si>
@@ -808,6 +649,42 @@
     <t>05</t>
   </si>
   <si>
+    <t>30038497</t>
+  </si>
+  <si>
+    <t>ABSORVENTE VEGETAL BOLSA 5KG</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002669281</t>
+  </si>
+  <si>
+    <t>20005074</t>
+  </si>
+  <si>
+    <t>Fenolftaleina</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>1002668394</t>
+  </si>
+  <si>
+    <t>20004936</t>
+  </si>
+  <si>
+    <t>Nitrato de Potasio</t>
+  </si>
+  <si>
+    <t>20004932</t>
+  </si>
+  <si>
+    <t>Nitrato de Plata</t>
+  </si>
+  <si>
     <t>20023885</t>
   </si>
   <si>
@@ -931,6 +808,30 @@
     <t>C/U</t>
   </si>
   <si>
+    <t>20005577</t>
+  </si>
+  <si>
+    <t>SPOTCHECK REVELADOR BLANCO 16 OZ MARCA M</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002667099</t>
+  </si>
+  <si>
+    <t>30006711</t>
+  </si>
+  <si>
+    <t>SKF RODAMIENTO. MODEL: 22215-EK</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002666229</t>
+  </si>
+  <si>
     <t>20020964</t>
   </si>
   <si>
@@ -961,6 +862,18 @@
     <t>1002660930</t>
   </si>
   <si>
+    <t>20006158</t>
+  </si>
+  <si>
+    <t>PAPEL LIMPIEZA TORK MOD. 420 A 1X525MTS</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002660931</t>
+  </si>
+  <si>
     <t>30008485</t>
   </si>
   <si>
@@ -982,6 +895,18 @@
     <t>C/U</t>
   </si>
   <si>
+    <t>20040973</t>
+  </si>
+  <si>
+    <t>ANTIEMPAÑANTE SPRAY PARA VISERAS Y GAFAS</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002654974</t>
+  </si>
+  <si>
     <t>20022101</t>
   </si>
   <si>
@@ -1042,6 +967,39 @@
     <t>C/U</t>
   </si>
   <si>
+    <t>20004998</t>
+  </si>
+  <si>
+    <t>ACIDO SULFURICO P.A.</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>1002648064</t>
+  </si>
+  <si>
+    <t>30053646</t>
+  </si>
+  <si>
+    <t>PERNO SUJECION CUERPO 3/8-18X4,5 P-6864</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002637281</t>
+  </si>
+  <si>
+    <t>30039714</t>
+  </si>
+  <si>
+    <t>ORING TAPA SILICONA #36 MOD220 U1 P-6864</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
     <t>20005224</t>
   </si>
   <si>
@@ -1064,6 +1022,30 @@
   </si>
   <si>
     <t>1002631449</t>
+  </si>
+  <si>
+    <t>20013978</t>
+  </si>
+  <si>
+    <t>PEPEL INDIC. ROLLO PH1-14 C/ESC. A COLOR</t>
+  </si>
+  <si>
+    <t>C/U</t>
+  </si>
+  <si>
+    <t>1002631450</t>
+  </si>
+  <si>
+    <t>20004877</t>
+  </si>
+  <si>
+    <t>CLOROFORMO   P.A.</t>
+  </si>
+  <si>
+    <t>20020860</t>
+  </si>
+  <si>
+    <t>REACTIVO COMBITITRANT 5 KARL FICHER</t>
   </si>
   <si>
     <t>30043362</t>
@@ -1191,7 +1173,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1"/>
   </sheetPr>
-  <dimension ref="A1:O100"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="9" customWidth="1"/>
@@ -1266,13 +1248,13 @@
         <v>16</v>
       </c>
       <c r="C2" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E2" s="4">
-        <v>46217</v>
+        <v>46206</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>18</v>
@@ -1313,13 +1295,13 @@
         <v>27</v>
       </c>
       <c r="C3" s="3">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="4">
-        <v>46216</v>
+        <v>46205</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>18</v>
@@ -1360,13 +1342,13 @@
         <v>31</v>
       </c>
       <c r="C4" s="3">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="4">
-        <v>46216</v>
+        <v>46205</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>18</v>
@@ -1407,22 +1389,22 @@
         <v>35</v>
       </c>
       <c r="C5" s="3">
-        <v>8</v>
+        <v>300</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E5" s="4">
-        <v>46216</v>
+        <v>46205</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>21</v>
@@ -1454,22 +1436,22 @@
         <v>39</v>
       </c>
       <c r="C6" s="3">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E6" s="4">
-        <v>46216</v>
+        <v>46204</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>21</v>
@@ -1495,28 +1477,28 @@
     </row>
     <row r="7" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="4">
+        <v>46204</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="3">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="4">
-        <v>46216</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>21</v>
@@ -1548,22 +1530,22 @@
         <v>46</v>
       </c>
       <c r="C8" s="3">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E8" s="4">
-        <v>46216</v>
+        <v>46204</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>21</v>
@@ -1595,22 +1577,22 @@
         <v>50</v>
       </c>
       <c r="C9" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E9" s="4">
-        <v>46216</v>
+        <v>46204</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>21</v>
@@ -1636,28 +1618,28 @@
     </row>
     <row r="10" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="3">
+        <v>36</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="3">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="4">
+        <v>46204</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="E10" s="4">
-        <v>46216</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>21</v>
@@ -1683,28 +1665,28 @@
     </row>
     <row r="11" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="3">
+        <v>20</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="3">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="4">
+        <v>46204</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="E11" s="4">
-        <v>46216</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>21</v>
@@ -1730,28 +1712,28 @@
     </row>
     <row r="12" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="3">
+        <v>28</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="3">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="E12" s="4">
-        <v>46216</v>
+        <v>46204</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>21</v>
@@ -1777,28 +1759,28 @@
     </row>
     <row r="13" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A13" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C13" s="3">
         <v>2</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E13" s="4">
-        <v>46216</v>
+        <v>46204</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>21</v>
@@ -1824,28 +1806,28 @@
     </row>
     <row r="14" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="3">
+        <v>40</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="3">
-        <v>2</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="E14" s="4">
-        <v>46216</v>
+        <v>46204</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>21</v>
@@ -1871,28 +1853,28 @@
     </row>
     <row r="15" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A15" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C15" s="3">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E15" s="4">
-        <v>46216</v>
+        <v>46204</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>21</v>
@@ -1918,28 +1900,28 @@
     </row>
     <row r="16" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A16" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C16" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E16" s="4">
-        <v>46216</v>
+        <v>46204</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>21</v>
@@ -1965,28 +1947,28 @@
     </row>
     <row r="17" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C17" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E17" s="4">
-        <v>46216</v>
+        <v>46204</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>21</v>
@@ -2012,28 +1994,28 @@
     </row>
     <row r="18" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C18" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E18" s="4">
-        <v>46216</v>
+        <v>46204</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>21</v>
@@ -2059,28 +2041,28 @@
     </row>
     <row r="19" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="4">
+        <v>46204</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="3">
-        <v>16</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="4">
-        <v>46216</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="H19" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>21</v>
@@ -2106,28 +2088,28 @@
     </row>
     <row r="20" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A20" s="2" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="3">
-        <v>32</v>
+      <c r="C20" s="5">
+        <v>10.000</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>88</v>
       </c>
       <c r="E20" s="4">
-        <v>46216</v>
+        <v>46204</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>21</v>
@@ -2153,28 +2135,28 @@
     </row>
     <row r="21" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C21" s="3">
-        <v>16</v>
+        <v>400</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E21" s="4">
-        <v>46216</v>
+        <v>46197</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>21</v>
@@ -2200,28 +2182,28 @@
     </row>
     <row r="22" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C22" s="3">
-        <v>16</v>
+        <v>250</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E22" s="4">
-        <v>46216</v>
+        <v>46197</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>21</v>
@@ -2247,28 +2229,28 @@
     </row>
     <row r="23" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A23" s="2" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C23" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E23" s="4">
-        <v>46216</v>
+        <v>46197</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>21</v>
@@ -2294,28 +2276,28 @@
     </row>
     <row r="24" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A24" s="2" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C24" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E24" s="4">
-        <v>46216</v>
+        <v>46197</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>21</v>
@@ -2341,28 +2323,28 @@
     </row>
     <row r="25" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A25" s="2" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C25" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E25" s="4">
-        <v>46216</v>
+        <v>46197</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>21</v>
@@ -2388,28 +2370,28 @@
     </row>
     <row r="26" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A26" s="2" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C26" s="3">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E26" s="4">
-        <v>46216</v>
+        <v>46197</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>21</v>
@@ -2435,28 +2417,28 @@
     </row>
     <row r="27" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A27" s="2" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C27" s="3">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E27" s="4">
-        <v>46216</v>
+        <v>46196</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>21</v>
@@ -2482,28 +2464,28 @@
     </row>
     <row r="28" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A28" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C28" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E28" s="4">
-        <v>46216</v>
+        <v>46191</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>21</v>
@@ -2529,28 +2511,28 @@
     </row>
     <row r="29" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A29" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C29" s="3">
         <v>2</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E29" s="4">
-        <v>46216</v>
+        <v>46191</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>21</v>
@@ -2576,28 +2558,28 @@
     </row>
     <row r="30" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A30" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C30" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E30" s="4">
-        <v>46216</v>
+        <v>46191</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>21</v>
@@ -2623,28 +2605,28 @@
     </row>
     <row r="31" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A31" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C31" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E31" s="4">
-        <v>46213</v>
+        <v>46191</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>21</v>
@@ -2659,10 +2641,10 @@
         <v>23</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>25</v>
@@ -2670,28 +2652,28 @@
     </row>
     <row r="32" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A32" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C32" s="3">
-        <v>3000</v>
+        <v>4</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E32" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>21</v>
@@ -2717,28 +2699,28 @@
     </row>
     <row r="33" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A33" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C33" s="3">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="4">
+        <v>46191</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E33" s="4">
-        <v>46211</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="H33" s="2" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>21</v>
@@ -2764,28 +2746,28 @@
     </row>
     <row r="34" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A34" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C34" s="5">
-        <v>50.000</v>
+        <v>136</v>
+      </c>
+      <c r="C34" s="3">
+        <v>20</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E34" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>21</v>
@@ -2811,28 +2793,28 @@
     </row>
     <row r="35" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A35" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C35" s="3">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E35" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>21</v>
@@ -2858,28 +2840,28 @@
     </row>
     <row r="36" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A36" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C36" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E36" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>21</v>
@@ -2905,28 +2887,28 @@
     </row>
     <row r="37" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A37" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C37" s="3">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E37" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>48</v>
+        <v>149</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>21</v>
@@ -2952,28 +2934,28 @@
     </row>
     <row r="38" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A38" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C38" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E38" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>21</v>
@@ -2999,28 +2981,28 @@
     </row>
     <row r="39" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A39" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C39" s="3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E39" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>56</v>
+        <v>157</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>21</v>
@@ -3046,28 +3028,28 @@
     </row>
     <row r="40" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A40" s="2" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C40" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E40" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>21</v>
@@ -3093,28 +3075,28 @@
     </row>
     <row r="41" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A41" s="2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C41" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="E41" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>64</v>
+        <v>165</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>21</v>
@@ -3140,28 +3122,28 @@
     </row>
     <row r="42" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A42" s="2" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C42" s="5">
-        <v>20.000</v>
+        <v>167</v>
+      </c>
+      <c r="C42" s="3">
+        <v>2</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="E42" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>21</v>
@@ -3187,28 +3169,28 @@
     </row>
     <row r="43" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A43" s="2" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="C43" s="3">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="E43" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>21</v>
@@ -3234,28 +3216,28 @@
     </row>
     <row r="44" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A44" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="C44" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="E44" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>21</v>
@@ -3281,28 +3263,28 @@
     </row>
     <row r="45" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A45" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="C45" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="E45" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>52</v>
+        <v>181</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>21</v>
@@ -3328,25 +3310,25 @@
     </row>
     <row r="46" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A46" s="2" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="C46" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E46" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>20</v>
@@ -3375,25 +3357,25 @@
     </row>
     <row r="47" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A47" s="2" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="C47" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="E47" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>33</v>
@@ -3422,28 +3404,28 @@
     </row>
     <row r="48" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A48" s="2" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="C48" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="E48" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>21</v>
@@ -3469,28 +3451,28 @@
     </row>
     <row r="49" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A49" s="2" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="C49" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="E49" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>21</v>
@@ -3516,28 +3498,28 @@
     </row>
     <row r="50" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A50" s="2" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C50" s="3">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="E50" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>21</v>
@@ -3563,28 +3545,28 @@
     </row>
     <row r="51" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A51" s="2" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="C51" s="3">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="E51" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>21</v>
@@ -3610,28 +3592,28 @@
     </row>
     <row r="52" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A52" s="2" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="C52" s="3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E52" s="4">
-        <v>46211</v>
+        <v>46191</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>21</v>
@@ -3657,28 +3639,28 @@
     </row>
     <row r="53" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A53" s="2" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C53" s="3">
         <v>20</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="E53" s="4">
-        <v>46206</v>
+        <v>46191</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>21</v>
@@ -3693,10 +3675,10 @@
         <v>23</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>24</v>
+        <v>211</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>25</v>
@@ -3704,25 +3686,25 @@
     </row>
     <row r="54" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A54" s="2" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="C54" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="E54" s="4">
-        <v>46205</v>
+        <v>46189</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>20</v>
@@ -3751,28 +3733,28 @@
     </row>
     <row r="55" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A55" s="2" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="C55" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="E55" s="4">
-        <v>46205</v>
+        <v>46188</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>21</v>
@@ -3798,25 +3780,25 @@
     </row>
     <row r="56" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A56" s="2" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C56" s="3">
-        <v>20</v>
+        <v>221</v>
+      </c>
+      <c r="C56" s="5">
+        <v>1.000</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>202</v>
+        <v>88</v>
       </c>
       <c r="E56" s="4">
-        <v>46204</v>
+        <v>46188</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>33</v>
@@ -3845,28 +3827,28 @@
     </row>
     <row r="57" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A57" s="2" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="C57" s="3">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="E57" s="4">
-        <v>46204</v>
+        <v>46188</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>21</v>
@@ -3892,28 +3874,28 @@
     </row>
     <row r="58" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A58" s="2" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C58" s="3">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="E58" s="4">
-        <v>46204</v>
+        <v>46185</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>21</v>
@@ -3939,28 +3921,28 @@
     </row>
     <row r="59" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A59" s="2" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="C59" s="3">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="E59" s="4">
-        <v>46204</v>
+        <v>46185</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>21</v>
@@ -3986,28 +3968,28 @@
     </row>
     <row r="60" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A60" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="C60" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="E60" s="4">
-        <v>46204</v>
+        <v>46185</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>21</v>
@@ -4033,28 +4015,28 @@
     </row>
     <row r="61" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A61" s="2" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="C61" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="E61" s="4">
-        <v>46197</v>
+        <v>46185</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>21</v>
@@ -4080,28 +4062,28 @@
     </row>
     <row r="62" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A62" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="C62" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="E62" s="4">
-        <v>46197</v>
+        <v>46185</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>21</v>
@@ -4127,28 +4109,28 @@
     </row>
     <row r="63" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A63" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C63" s="3">
+        <v>5</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E63" s="4">
+        <v>46185</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C63" s="3">
-        <v>4</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E63" s="4">
-        <v>46197</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>225</v>
-      </c>
       <c r="H63" s="2" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>21</v>
@@ -4174,28 +4156,28 @@
     </row>
     <row r="64" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A64" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C64" s="3">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E64" s="4">
-        <v>46197</v>
+        <v>46185</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>21</v>
@@ -4221,28 +4203,28 @@
     </row>
     <row r="65" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A65" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C65" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E65" s="4">
-        <v>46196</v>
+        <v>46185</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>21</v>
@@ -4268,28 +4250,28 @@
     </row>
     <row r="66" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A66" s="2" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="C66" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="E66" s="4">
-        <v>46191</v>
+        <v>46185</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>21</v>
@@ -4315,28 +4297,28 @@
     </row>
     <row r="67" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A67" s="2" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="C67" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="E67" s="4">
-        <v>46191</v>
+        <v>46185</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>21</v>
@@ -4362,28 +4344,28 @@
     </row>
     <row r="68" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A68" s="2" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C68" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="E68" s="4">
-        <v>46191</v>
+        <v>46185</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>21</v>
@@ -4409,19 +4391,19 @@
     </row>
     <row r="69" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A69" s="2" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C69" s="3">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="E69" s="4">
-        <v>46191</v>
+        <v>46185</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>18</v>
@@ -4430,7 +4412,7 @@
         <v>249</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>21</v>
@@ -4456,19 +4438,19 @@
     </row>
     <row r="70" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A70" s="2" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C70" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="E70" s="4">
-        <v>46191</v>
+        <v>46185</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>18</v>
@@ -4477,7 +4459,7 @@
         <v>249</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>33</v>
+        <v>153</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>21</v>
@@ -4503,28 +4485,28 @@
     </row>
     <row r="71" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A71" s="2" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C71" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="E71" s="4">
-        <v>46191</v>
+        <v>46185</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>21</v>
@@ -4550,28 +4532,28 @@
     </row>
     <row r="72" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A72" s="2" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="C72" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="E72" s="4">
-        <v>46191</v>
+        <v>46184</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>21</v>
@@ -4586,10 +4568,10 @@
         <v>23</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>24</v>
+        <v>211</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>25</v>
@@ -4597,25 +4579,25 @@
     </row>
     <row r="73" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A73" s="2" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="C73" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="E73" s="4">
-        <v>46191</v>
+        <v>46182</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>33</v>
@@ -4633,10 +4615,10 @@
         <v>23</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>264</v>
+        <v>24</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>25</v>
@@ -4644,28 +4626,28 @@
     </row>
     <row r="74" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A74" s="2" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C74" s="3">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="E74" s="4">
-        <v>46185</v>
+        <v>46182</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>21</v>
@@ -4691,28 +4673,28 @@
     </row>
     <row r="75" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A75" s="2" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C75" s="3">
-        <v>40</v>
+        <v>281</v>
+      </c>
+      <c r="C75" s="5">
+        <v>108.000</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>271</v>
+        <v>88</v>
       </c>
       <c r="E75" s="4">
-        <v>46185</v>
+        <v>46178</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>21</v>
@@ -4738,28 +4720,28 @@
     </row>
     <row r="76" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A76" s="2" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="C76" s="3">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E76" s="4">
-        <v>46185</v>
+        <v>46178</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>21</v>
@@ -4785,28 +4767,28 @@
     </row>
     <row r="77" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A77" s="2" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="C77" s="3">
         <v>4</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="E77" s="4">
-        <v>46185</v>
+        <v>46171</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>21</v>
@@ -4832,28 +4814,28 @@
     </row>
     <row r="78" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A78" s="2" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="C78" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="E78" s="4">
-        <v>46185</v>
+        <v>46171</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>21</v>
@@ -4879,28 +4861,28 @@
     </row>
     <row r="79" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A79" s="2" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="C79" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="E79" s="4">
-        <v>46185</v>
+        <v>46171</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>21</v>
@@ -4926,28 +4908,28 @@
     </row>
     <row r="80" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A80" s="2" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="C80" s="3">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="E80" s="4">
-        <v>46185</v>
+        <v>46162</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>268</v>
+        <v>301</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>21</v>
@@ -4973,28 +4955,28 @@
     </row>
     <row r="81" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A81" s="2" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="C81" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="E81" s="4">
-        <v>46185</v>
+        <v>46162</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>21</v>
@@ -5020,28 +5002,28 @@
     </row>
     <row r="82" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A82" s="2" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="C82" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="E82" s="4">
-        <v>46185</v>
+        <v>46162</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>21</v>
@@ -5067,28 +5049,28 @@
     </row>
     <row r="83" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A83" s="2" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="C83" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="E83" s="4">
-        <v>46185</v>
+        <v>46162</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>21</v>
@@ -5114,28 +5096,28 @@
     </row>
     <row r="84" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A84" s="2" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="C84" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="E84" s="4">
-        <v>46185</v>
+        <v>46162</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>21</v>
@@ -5161,28 +5143,28 @@
     </row>
     <row r="85" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A85" s="2" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="C85" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="E85" s="4">
-        <v>46185</v>
+        <v>46162</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>21</v>
@@ -5208,28 +5190,28 @@
     </row>
     <row r="86" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A86" s="2" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="C86" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="E86" s="4">
-        <v>46185</v>
+        <v>46162</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>21</v>
@@ -5255,28 +5237,28 @@
     </row>
     <row r="87" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A87" s="2" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="C87" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E87" s="4">
-        <v>46182</v>
+        <v>46148</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>21</v>
@@ -5302,28 +5284,28 @@
     </row>
     <row r="88" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A88" s="2" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="C88" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="E88" s="4">
-        <v>46182</v>
+        <v>46148</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>21</v>
@@ -5349,28 +5331,28 @@
     </row>
     <row r="89" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A89" s="2" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C89" s="5">
-        <v>108.000</v>
+        <v>330</v>
+      </c>
+      <c r="C89" s="3">
+        <v>2</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>131</v>
+        <v>331</v>
       </c>
       <c r="E89" s="4">
-        <v>46178</v>
+        <v>46148</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>21</v>
@@ -5396,28 +5378,28 @@
     </row>
     <row r="90" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A90" s="2" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="C90" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="E90" s="4">
-        <v>46171</v>
+        <v>46140</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>21</v>
@@ -5443,28 +5425,28 @@
     </row>
     <row r="91" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A91" s="2" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="C91" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="E91" s="4">
-        <v>46171</v>
+        <v>46140</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>21</v>
@@ -5490,28 +5472,28 @@
     </row>
     <row r="92" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A92" s="2" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="C92" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E92" s="4">
-        <v>46162</v>
+        <v>46140</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>21</v>
@@ -5537,28 +5519,28 @@
     </row>
     <row r="93" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A93" s="2" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="C93" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="E93" s="4">
-        <v>46162</v>
+        <v>46140</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>21</v>
@@ -5584,28 +5566,28 @@
     </row>
     <row r="94" outlineLevel="0" collapsed="0" hidden="0">
       <c r="A94" s="2" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="C94" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="E94" s="4">
-        <v>46162</v>
+        <v>46031</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>21</v>
@@ -5626,288 +5608,6 @@
         <v>24</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="95" outlineLevel="0" collapsed="0" hidden="0">
-      <c r="A95" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C95" s="3">
-        <v>5</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E95" s="4">
-        <v>46162</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J95" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K95" s="4">
-        <v/>
-      </c>
-      <c r="L95" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M95" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O95" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="96" outlineLevel="0" collapsed="0" hidden="0">
-      <c r="A96" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="C96" s="3">
-        <v>4</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E96" s="4">
-        <v>46162</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J96" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K96" s="4">
-        <v/>
-      </c>
-      <c r="L96" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M96" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N96" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O96" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="97" outlineLevel="0" collapsed="0" hidden="0">
-      <c r="A97" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C97" s="3">
-        <v>8</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E97" s="4">
-        <v>46162</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J97" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K97" s="4">
-        <v/>
-      </c>
-      <c r="L97" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M97" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N97" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O97" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="98" outlineLevel="0" collapsed="0" hidden="0">
-      <c r="A98" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="C98" s="3">
-        <v>2</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E98" s="4">
-        <v>46148</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J98" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K98" s="4">
-        <v/>
-      </c>
-      <c r="L98" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M98" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N98" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O98" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="99" outlineLevel="0" collapsed="0" hidden="0">
-      <c r="A99" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C99" s="3">
-        <v>3</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="E99" s="4">
-        <v>46140</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I99" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J99" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K99" s="4">
-        <v/>
-      </c>
-      <c r="L99" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M99" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N99" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O99" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="100" outlineLevel="0" collapsed="0" hidden="0">
-      <c r="A100" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C100" s="3">
-        <v>3</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E100" s="4">
-        <v>46031</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J100" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K100" s="4">
-        <v/>
-      </c>
-      <c r="L100" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M100" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N100" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O100" s="2" t="s">
         <v>25</v>
       </c>
     </row>
